--- a/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/bio-bio.xlsx
+++ b/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/bio-bio.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>77972.47</v>
+        <v>76912.39</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>2463.27</v>
+        <v>2490.82</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>2463.27</v>
+        <v>2457.68</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>67074.3</v>
+        <v>67336.13</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>5330.25</v>
+        <v>5341.61</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>40097.65</v>
+        <v>39454.74</v>
       </c>
     </row>
   </sheetData>
